--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486287_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486287_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8088</v>
+        <v>8.0534</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5939</v>
+        <v>3.6015</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2149</v>
+        <v>4.452</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7342</v>
+        <v>3.4152</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3787</v>
+        <v>1.3593</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3554</v>
+        <v>2.0559</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1789</v>
+        <v>2.5134</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9111</v>
+        <v>1.8432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2677</v>
+        <v>0.6702</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5553</v>
+        <v>0.9019</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5324</v>
+        <v>-0.4838</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0877</v>
+        <v>1.3857</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0875</v>
+        <v>3.0451</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1751</v>
+        <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3568</v>
+        <v>-0.1018</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3073</v>
+        <v>-0.3893</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0495</v>
+        <v>0.2875</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3698</v>
+        <v>1.695</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.669</v>
+        <v>5.9568</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3095</v>
+        <v>2.6962</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3595</v>
+        <v>3.2605</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4152</v>
+        <v>4.9077</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3593</v>
+        <v>1.9163</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0559</v>
+        <v>2.9914</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5134</v>
+        <v>4.4369</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8432</v>
+        <v>2.5977</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6702</v>
+        <v>1.8392</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9019</v>
+        <v>0.4708</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4838</v>
+        <v>-0.6814</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3857</v>
+        <v>1.1522</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0451</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2626</v>
+        <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4863</v>
+        <v>0.6363</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6813</v>
+        <v>0.2392</v>
       </c>
       <c r="U3" t="n">
-        <v>0.195</v>
+        <v>0.3972</v>
       </c>
       <c r="V3" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4798</v>
+        <v>5.7077</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4042</v>
+        <v>2.986</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0756</v>
+        <v>2.7217</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9077</v>
+        <v>3.7342</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9163</v>
+        <v>2.3787</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9914</v>
+        <v>1.3554</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4369</v>
+        <v>3.1789</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5977</v>
+        <v>2.9111</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8392</v>
+        <v>0.2677</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4708</v>
+        <v>0.5553</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6814</v>
+        <v>-0.5324</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1522</v>
+        <v>1.0877</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1593</v>
+        <v>1.2558</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0529</v>
+        <v>0.6994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2122</v>
+        <v>0.5564</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W4" t="n">
         <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3995</v>
+        <v>3.9652</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5053</v>
+        <v>1.1326</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8942</v>
+        <v>2.8325</v>
       </c>
       <c r="G5" t="n">
         <v>2.9682</v>
@@ -844,13 +844,13 @@
         <v>2.8276</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6562</v>
+        <v>-1.0905</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3699</v>
+        <v>-0.7426</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2863</v>
+        <v>-0.3479</v>
       </c>
       <c r="V5" t="n">
         <v>0.5649999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1089</v>
+        <v>1.6635</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>-1.8324</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7789</v>
+        <v>3.4959</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2506</v>
+        <v>0.2043</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9885</v>
+        <v>-1.7822</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2621</v>
+        <v>1.9866</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6124000000000001</v>
+        <v>-0.829</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4594</v>
+        <v>-1.2164</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153</v>
+        <v>0.3873</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6382</v>
+        <v>1.0334</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5291</v>
+        <v>-0.5659</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1091</v>
+        <v>1.5993</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5533</v>
+        <v>0.1541</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0227</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4694</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3792</v>
+        <v>1.4067</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9009</v>
+        <v>-0.4956</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2802</v>
+        <v>1.9022</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2043</v>
+        <v>1.2506</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7822</v>
+        <v>0.9885</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9866</v>
+        <v>0.2621</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.829</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2164</v>
+        <v>0.4594</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3873</v>
+        <v>0.153</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0334</v>
+        <v>0.6382</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5659</v>
+        <v>0.5291</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5993</v>
+        <v>0.1091</v>
       </c>
       <c r="P7" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1301</v>
+        <v>-0.149</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0156</v>
+        <v>0.1971</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1458</v>
+        <v>-0.3461</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8474</v>
+        <v>1.1779</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2244</v>
+        <v>-0.7088</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0717</v>
+        <v>1.8868</v>
       </c>
       <c r="G8" t="n">
         <v>0.6946</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.3443</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7294</v>
+        <v>-0.2139</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0545</v>
+        <v>-0.1304</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5137</v>
+        <v>0.0519</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5851</v>
+        <v>-1.9578</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0714</v>
+        <v>2.0097</v>
       </c>
       <c r="G9" t="n">
         <v>1.3599</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5686</v>
+        <v>-0.003</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0577</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1163</v>
+        <v>0.0547</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.873</v>
+        <v>-0.6311</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6285</v>
+        <v>-1.4482</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.8172</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1983</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.3251</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0565</v>
+        <v>0.1238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5105</v>
+        <v>-0.4488</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7141</v>
+        <v>-3.0752</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2825</v>
+        <v>-4.767</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5684</v>
+        <v>1.6917</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2857</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2108</v>
+        <v>-0.572</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9589</v>
+        <v>-0.4434</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2519</v>
+        <v>-0.1286</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.7828</v>
+        <v>20.4678</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.429</v>
+        <v>-1.743999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>22.2119</v>
+        <v>22.2118</v>
       </c>
       <c r="G13" t="n">
         <v>16.2722</v>
       </c>
       <c r="H13" t="n">
-        <v>4.897099999999998</v>
+        <v>4.8971</v>
       </c>
       <c r="I13" t="n">
         <v>11.3751</v>
@@ -1447,7 +1447,7 @@
         <v>6.906000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>3.155700000000001</v>
+        <v>3.1557</v>
       </c>
       <c r="M13" t="n">
         <v>6.2104</v>
@@ -1468,13 +1468,13 @@
         <v>22.8384</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.43</v>
+        <v>-0.745</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3938</v>
+        <v>-0.7088000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.03639999999999977</v>
+        <v>-0.03599999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>-3.7597</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7111</v>
+        <v>1.8797</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1317</v>
+        <v>1.4254</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8428</v>
+        <v>0.4543</v>
       </c>
       <c r="G14" t="n">
-        <v>0.18</v>
+        <v>-0.3146</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1035</v>
+        <v>1.0767</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0765</v>
+        <v>-1.3913</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4574</v>
+        <v>1.5415</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5538</v>
+        <v>2.7041</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.0112</v>
+        <v>-1.1626</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6373</v>
+        <v>-1.8561</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4504</v>
+        <v>-1.6274</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0877</v>
+        <v>-0.2287</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.305</v>
+        <v>-3.6976</v>
       </c>
       <c r="R14" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9216</v>
+        <v>0.4792</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6307</v>
+        <v>-0.0036</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2909</v>
+        <v>0.4828</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3904</v>
+        <v>3.0202</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.5851</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1764</v>
+        <v>1.0839</v>
       </c>
       <c r="E15" t="n">
         <v>1.6664</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.49</v>
+        <v>-0.5825</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5108</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7519</v>
+        <v>0.6594</v>
       </c>
       <c r="T15" t="n">
         <v>0.5516</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2003</v>
+        <v>0.1078</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3698</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8457</v>
+        <v>1.0342</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0902</v>
+        <v>-1.1375</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2445</v>
+        <v>2.1717</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3146</v>
+        <v>0.18</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0767</v>
+        <v>0.1035</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3913</v>
+        <v>0.0765</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5415</v>
+        <v>-0.4574</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7041</v>
+        <v>0.5538</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1626</v>
+        <v>-1.0112</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8561</v>
+        <v>0.6373</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6274</v>
+        <v>-0.4504</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2287</v>
+        <v>1.0877</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-3.6976</v>
-      </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5548</v>
+        <v>1.2447</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3389</v>
+        <v>0.6249</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.216</v>
+        <v>0.6198</v>
       </c>
       <c r="V16" t="n">
-        <v>3.0202</v>
+        <v>-0.3904</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5851</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.833</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8471</v>
+        <v>-2.7354</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2106</v>
+        <v>1.9023</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7255</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5239</v>
+        <v>0.3275</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.5582</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5189</v>
+        <v>-1.2338</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4946</v>
+        <v>-1.2711</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0243</v>
+        <v>0.0373</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6335</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2329</v>
+        <v>0.0523</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0411</v>
+        <v>0.1027</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9711</v>
+        <v>-1.7782</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7278</v>
+        <v>-1.4948</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7567</v>
+        <v>-0.2834</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3017</v>
+        <v>-1.9848</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4148</v>
+        <v>-0.6141</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1131</v>
+        <v>-1.3706</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0274</v>
+        <v>0.0179</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1804</v>
+        <v>0.6482</v>
       </c>
       <c r="L19" t="n">
-        <v>0.153</v>
+        <v>-0.6303</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2742</v>
+        <v>-2.0027</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2344</v>
+        <v>-1.2624</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0399</v>
+        <v>-0.7403</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>-1.5225</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>2.0706</v>
+        <v>0.0766</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5622</v>
+        <v>-0.5552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5084</v>
+        <v>0.6318</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0467</v>
+        <v>-2.401</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8301</v>
+        <v>-2.5091</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2166</v>
+        <v>0.1081</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9848</v>
+        <v>-2.8874</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6141</v>
+        <v>-0.4291</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3706</v>
+        <v>-2.4583</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0179</v>
+        <v>-2.0657</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6482</v>
+        <v>0.0547</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6303</v>
+        <v>-2.1204</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0027</v>
+        <v>-0.8217</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2624</v>
+        <v>-0.4838</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7403</v>
+        <v>-0.3379</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1919</v>
+        <v>-0.3836</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6985</v>
+        <v>0.0598</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8789</v>
+        <v>-2.9935</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9561</v>
+        <v>-4.6219</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07729999999999999</v>
+        <v>1.6283</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8874</v>
+        <v>-2.3017</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4291</v>
+        <v>-2.4148</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4583</v>
+        <v>0.1131</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0657</v>
+        <v>-2.0274</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0547</v>
+        <v>-2.1804</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1204</v>
+        <v>0.153</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8217</v>
+        <v>-0.2742</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4838</v>
+        <v>-0.2344</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3379</v>
+        <v>-0.0399</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8615</v>
+        <v>1.0482</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8904</v>
+        <v>0.6682</v>
       </c>
       <c r="U21" t="n">
-        <v>0.029</v>
+        <v>0.38</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2885</v>
+        <v>-3.1202</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8871</v>
+        <v>-4.7754</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5986</v>
+        <v>1.6552</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5427</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3957</v>
+        <v>-0.2274</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2824</v>
+        <v>-0.1706</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1133</v>
+        <v>-0.0568</v>
       </c>
       <c r="V22" t="n">
         <v>2.2599</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.269</v>
+        <v>-4.7285</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.031</v>
+        <v>-3.2806</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.238</v>
+        <v>-1.4479</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5174</v>
+        <v>-1.034</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1792</v>
+        <v>-1.1224</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6966</v>
+        <v>0.0885</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8924</v>
+        <v>1.6007</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2775</v>
+        <v>0.2404</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.1698</v>
+        <v>1.3603</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.625</v>
+        <v>-2.6346</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0983</v>
+        <v>-1.3628</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5268</v>
+        <v>-1.2718</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2175</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.5225</v>
+        <v>-4.7852</v>
       </c>
       <c r="R23" t="n">
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4041</v>
+        <v>-0.0192</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1887</v>
+        <v>-0.0961</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5928</v>
+        <v>0.0769</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9064</v>
+        <v>-5.2023</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0629</v>
+        <v>-3.4781</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8435</v>
+        <v>-1.7242</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.034</v>
+        <v>-3.5174</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1224</v>
+        <v>0.1792</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0885</v>
+        <v>-3.6966</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6007</v>
+        <v>-1.8924</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2404</v>
+        <v>1.2775</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3603</v>
+        <v>-3.1698</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6346</v>
+        <v>-1.625</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3628</v>
+        <v>-1.0983</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2718</v>
+        <v>-0.5268</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4801</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7852</v>
+        <v>-1.5225</v>
       </c>
       <c r="R24" t="n">
         <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1971</v>
+        <v>-0.3374</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8784</v>
+        <v>-0.2584</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3187</v>
+        <v>-0.079</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.7829</v>
+        <v>-18.2927</v>
       </c>
       <c r="E25" t="n">
-        <v>-22.2118</v>
+        <v>-22.2121</v>
       </c>
       <c r="F25" t="n">
-        <v>2.429100000000001</v>
+        <v>3.9192</v>
       </c>
       <c r="G25" t="n">
         <v>-16.2724</v>
@@ -2404,13 +2404,13 @@
         <v>14.1377</v>
       </c>
       <c r="S25" t="n">
-        <v>1.429999999999999</v>
+        <v>2.9203</v>
       </c>
       <c r="T25" t="n">
-        <v>0.03620000000000023</v>
+        <v>0.0361999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3938</v>
+        <v>2.884</v>
       </c>
       <c r="V25" t="n">
         <v>3.7597</v>
